--- a/stories/arbres/ATOM-EMO.LEX.010-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam range ses cubes avec maman. La tour tombe. Adam recommence. Il pose un cube. Encore un. La tour tient. Adam sourit. Il dit : je suis fier. Maman dit : fier de ton effort. Pas meilleur que l'autre. Adam dit : mon effort. Il a recommencé. Maman applaudit tout doux. Adam est fier de son effort. Il range le dernier cube.</t>
+          <t>Adam range ses cubes avec maman. La tour tombe. Adam recommence. Il pose un cube. Encore un. La tour tient. Adam sourit. Je suis fier. Fier de ton effort. Pas meilleur que l'autre. Mon effort. Il a recommencé. Maman applaudit tout doux. Adam est fier de son effort. Il range le dernier cube.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Adam range ses cubes avec maman. La tour tombe. Adam recommence. Il pose un cube. Encore un. La tour tient. Adam sourit.
+narrateur|Je suis fier.
+maman|Fier de ton effort. Pas meilleur que l'autre.
+enfant-m|Mon effort. Il a recommencé. Maman applaudit tout doux.
+narrateur|Adam est fier de son effort. Il range le dernier cube.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1492,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La tour tient. Quelle émotion ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1521,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam a dit : je suis fier. C'était son effort.</t>
+          <t>Adam Je suis fier. C'était son effort.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1663,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam
+enfant-f|Je suis fier. C'était son effort.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman baisse la lumière. Adam souffle.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.010-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Adam est fier de son effort. Il range le dernier cube.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|La tour tient. Quelle émotion ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
 enfant-f|Je suis fier. C'était son effort.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Maman baisse la lumière. Adam souffle.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.010-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adam est fier de son effort</t>
+          <t>La tour d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La tour d'Amir tombe. Il recommence. Elle tient. Il est fier de son effort, pas meilleur que l'autre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam range ses cubes avec maman. La tour tombe. Adam recommence. Il pose un cube. Encore un. La tour tient. Adam sourit. Je suis fier. Fier de ton effort. Pas meilleur que l'autre. Mon effort. Il a recommencé. Maman applaudit tout doux. Adam est fier de son effort. Il range le dernier cube.</t>
+          <t>Le panier en osier craque tout doux. Dedans, des cubes de bois, bien lisses. Un cube est rouge. Un cube est bleu. La lampe a un abat-jour jaune. Elle fait un rond de lumière sur le tapis. La chambre sent le bois, un peu. Amir, tu sors les cubes ? Oui, maman. Ils sont lisses. On range après. D'abord on construit. En ce moment, Amir pose un cube. Puis un autre. Puis encore un. La tour monte, tout doucement. Elle est haute, maman. Elle est haute, oui. Tout doux. Un cube glisse. La tour tombe. Les cubes tapent le tapis, tout bas. Elle est tombée. Tu peux recommencer. Un cube. Puis un autre. Amir recommence. Il pose un cube rouge. Encore un, bleu. Encore un, jaune. Elle tient, cette fois. Elle tient. Tu as recommencé. Amir sent sa poitrine chaude. Un sourire arrive, tout seul. Je suis fier. Fier de ton effort. Pas meilleur que l'autre. Mon effort. J'ai recommencé. Bravo, Amir. C'est du bon travail. Tu as posé cube après cube. La tour tient. Tu veux poser le dernier cube ? Le petit, tout en haut. Amir pose le dernier cube. La tour reste debout, dans la lumière. Tu es fier de ton effort ? Oui. Fier. Pas meilleur que l'autre. On nomme l'effort. On nomme fier. Maman applaudit tout doux. Les mains font un petit bruit. J'ai recommencé. La tour tient. Oui. C'est ça, l'effort. On range le dernier cube, après ? Encore un moment. Elle est belle. Elle est belle, oui. Ton effort aussi. Le cube rouge est en bas. Tu l'as vu ? Oui. Le bleu est au milieu. Tu as choisi. Cube après cube. Le rond de lumière reste sur le tapis. Le panier en osier attend à côté. Un cube resté dedans tapote un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Adam range ses cubes avec maman. La tour tombe. Adam recommence. Il pose un cube. Encore un. La tour tient. Adam sourit.
-narrateur|Je suis fier.
-maman|Fier de ton effort. Pas meilleur que l'autre.
-enfant-m|Mon effort. Il a recommencé. Maman applaudit tout doux.
-narrateur|Adam est fier de son effort. Il range le dernier cube.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le panier en osier craque tout doux.
+narrateur|Dedans, des cubes de bois, bien lisses.
+narrateur|Un cube est rouge. Un cube est bleu.
+narrateur|La lampe a un abat-jour jaune.
+narrateur|Elle fait un rond de lumière sur le tapis.
+narrateur|La chambre sent le bois, un peu.
+maman|Amir, tu sors les cubes ?
+enfant-m|Oui, maman. Ils sont lisses.
+maman|On range après. D'abord on construit.
+narrateur|En ce moment, Amir pose un cube.
+narrateur|Puis un autre. Puis encore un.
+narrateur|La tour monte, tout doucement.
+enfant-m|Elle est haute, maman.
+maman|Elle est haute, oui. Tout doux.
+narrateur|Un cube glisse. La tour tombe.
+narrateur|Les cubes tapent le tapis, tout bas.
+enfant-m|Elle est tombée.
+maman|Tu peux recommencer. Un cube. Puis un autre.
+narrateur|Amir recommence.
+narrateur|Il pose un cube rouge.
+narrateur|Encore un, bleu. Encore un, jaune.
+enfant-m|Elle tient, cette fois.
+maman|Elle tient. Tu as recommencé.
+narrateur|Amir sent sa poitrine chaude.
+narrateur|Un sourire arrive, tout seul.
+enfant-m|Je suis fier.
+maman|Fier de ton effort.
+maman|Pas meilleur que l'autre.
+enfant-m|Mon effort. J'ai recommencé.
+maman|Bravo, Amir. C'est du bon travail.
+maman|Tu as posé cube après cube.
+enfant-m|La tour tient.
+maman|Tu veux poser le dernier cube ?
+enfant-m|Le petit, tout en haut.
+narrateur|Amir pose le dernier cube.
+narrateur|La tour reste debout, dans la lumière.
+maman|Tu es fier de ton effort ?
+enfant-m|Oui. Fier. Pas meilleur que l'autre.
+maman|On nomme l'effort. On nomme fier.
+narrateur|Maman applaudit tout doux.
+narrateur|Les mains font un petit bruit.
+enfant-m|J'ai recommencé. La tour tient.
+maman|Oui. C'est ça, l'effort.
+maman|On range le dernier cube, après ?
+enfant-m|Encore un moment. Elle est belle.
+maman|Elle est belle, oui. Ton effort aussi.
+maman|Le cube rouge est en bas. Tu l'as vu ?
+enfant-m|Oui. Le bleu est au milieu.
+maman|Tu as choisi. Cube après cube.
+narrateur|Le rond de lumière reste sur le tapis.
+narrateur|Le panier en osier attend à côté.
+narrateur|Un cube resté dedans tapote un peu.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cubes_bois,panier_osier</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,7 +1563,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La tour tient. Quelle émotion ?</t>
+          <t>narrateur|La tour tient.
+narrateur|Quelle émotion ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam Je suis fier. C'était son effort.</t>
+          <t>Amir a nommé : fier. C'était son effort. Je suis fier de mon effort. Oui. Tu as recommencé. Pas meilleur que l'autre. Bravo. C'est du bon travail. La tour tient. Mon effort. Tu veux encore dire le mot ? Fier. Le dernier cube reste en haut. Le bois est lisse sous les doigts.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,11 +1736,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Adam
-enfant-f|Je suis fier. C'était son effort.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir a nommé : fier.
+narrateur|C'était son effort.
+enfant-m|Je suis fier de mon effort.
+maman|Oui. Tu as recommencé.
+maman|Pas meilleur que l'autre.
+maman|Bravo. C'est du bon travail.
+enfant-m|La tour tient. Mon effort.
+maman|Tu veux encore dire le mot ?
+enfant-m|Fier.
+narrateur|Le dernier cube reste en haut.
+narrateur|Le bois est lisse sous les doigts.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>cubes_bois</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1701,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman baisse la lumière. Adam souffle.</t>
+          <t>Maman baisse un peu la lumière. Tu souffles, Amir ? Oui. La tour reste debout. On la laisse jusqu'au dîner ? Oui. Je suis encore fier. Bravo. Ton effort est là. Amir souffle. Le panier en osier est calme. Les cubes restés dedans ne bougent plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,10 +1914,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman baisse la lumière. Adam souffle.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman baisse un peu la lumière.
+maman|Tu souffles, Amir ?
+enfant-m|Oui. La tour reste debout.
+maman|On la laisse jusqu'au dîner ?
+enfant-m|Oui. Je suis encore fier.
+maman|Bravo. Ton effort est là.
+narrateur|Amir souffle.
+narrateur|Le panier en osier est calme.
+narrateur|Les cubes restés dedans ne bougent plus.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1865,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais fier de mon effort. Tu as recommencé. Bravo. La tour reste debout, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,7 +2094,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais fier de mon effort.
+maman|Tu as recommencé. Bravo.
+narrateur|La tour reste debout, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2027,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2157,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.010-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le panier en osier craque tout doux. Dedans, des cubes de bois, bien lisses. Un cube est rouge. Un cube est bleu. La lampe a un abat-jour jaune. Elle fait un rond de lumière sur le tapis. La chambre sent le bois, un peu. Amir, tu sors les cubes ? Oui, maman. Ils sont lisses. On range après. D'abord on construit. En ce moment, Amir pose un cube. Puis un autre. Puis encore un. La tour monte, tout doucement. Elle est haute, maman. Elle est haute, oui. Tout doux. Un cube glisse. La tour tombe. Les cubes tapent le tapis, tout bas. Elle est tombée. Tu peux recommencer. Un cube. Puis un autre. Amir recommence. Il pose un cube rouge. Encore un, bleu. Encore un, jaune. Elle tient, cette fois. Elle tient. Tu as recommencé. Amir sent sa poitrine chaude. Un sourire arrive, tout seul. Je suis fier. Fier de ton effort. Pas meilleur que l'autre. Mon effort. J'ai recommencé. Bravo, Amir. C'est du bon travail. Tu as posé cube après cube. La tour tient. Tu veux poser le dernier cube ? Le petit, tout en haut. Amir pose le dernier cube. La tour reste debout, dans la lumière. Tu es fier de ton effort ? Oui. Fier. Pas meilleur que l'autre. On nomme l'effort. On nomme fier. Maman applaudit tout doux. Les mains font un petit bruit. J'ai recommencé. La tour tient. Oui. C'est ça, l'effort. On range le dernier cube, après ? Encore un moment. Elle est belle. Elle est belle, oui. Ton effort aussi. Le cube rouge est en bas. Tu l'as vu ? Oui. Le bleu est au milieu. Tu as choisi. Cube après cube. Le rond de lumière reste sur le tapis. Le panier en osier attend à côté. Un cube resté dedans tapote un peu.</t>
+          <t>Le panier en osier craque tout doux. Dedans, des cubes de bois, bien lisses. Un cube est rouge. Un cube est bleu. La lampe a un abat-jour jaune. Elle fait un rond de lumière sur le tapis. La chambre sent le bois, un peu. Amir, tu sors les cubes ? Oui, maman. Ils sont lisses. On range après. D'abord on construit. En ce moment, Amir pose un cube. Puis un autre. Puis encore un. La tour monte, tout doucement. Elle est haute, maman. Elle est haute, oui. Tout doux. Un cube glisse. La tour tombe. Les cubes tapent le tapis, tout bas. Elle est tombée. Tu peux recommencer. Un cube. Puis un autre. Amir recommence. Il pose un cube rouge. Encore un, bleu. Encore un, jaune. Elle tient, cette fois. Elle tient. Tu as recommencé. Amir sent sa poitrine chaude. Un sourire arrive, tout seul. Je suis fier. Fier de ton effort. Pas meilleur que l'autre. Mon effort. J'ai recommencé. Tu as posé cube après cube. La tour tient. Tu veux poser le dernier cube ? Le petit, tout en haut. Amir pose le dernier cube. La tour reste debout, dans la lumière. Tu es fier de ton effort ? Oui. Fier. Pas meilleur que l'autre. On nomme l'effort. On nomme fier. Maman applaudit tout doux. Les mains font un petit bruit. J'ai recommencé. La tour tient. Oui. C'est ça, l'effort. On range le dernier cube, après ? Encore un moment. Elle est belle. Elle est belle, oui. Ton effort aussi. Le cube rouge est en bas. Tu l'as vu ? Oui. Le bleu est au milieu. Tu as choisi. Cube après cube. Le rond de lumière reste sur le tapis. Le panier en osier attend à côté. Un cube resté dedans tapote un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam range ses cubes avec maman. La tour tombe. Adam recommence. Il pose un cube. Encore un. La tour tient. Adam sourit. Il dit : je suis &lt;emphasis level="moderate"&gt;fier&lt;/emphasis&gt;. Maman dit : fier de ton effort. Pas meilleur que l'autre. Adam dit : mon effort. Il a recommencé. Maman applaudit tout doux. Adam est fier de son effort. Il range le dernier cube.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le panier en osier craque tout doux. Dedans, des cubes de bois, bien lisses. Un cube est rouge. Un cube est bleu. La lampe a un abat-jour jaune. Elle fait un rond de lumière sur le tapis. La chambre sent le bois, un peu. Amir, tu sors les cubes ? Oui, maman. Ils sont lisses. On range après. D'abord on construit. En ce moment, Amir pose un cube. Puis un autre. Puis encore un. La tour monte, tout doucement. Elle est haute, maman. Elle est haute, oui. Tout doux. Un cube glisse. La tour tombe. Les cubes tapent le tapis, tout bas. Elle est tombée. Tu peux recommencer. Un cube. Puis un autre. Amir recommence. Il pose un cube rouge. Encore un, bleu. Encore un, jaune. Elle tient, cette fois. Elle tient. Tu as recommencé. Amir sent sa poitrine chaude. Un sourire arrive, tout seul. Je suis fier. Fier de ton effort. Pas meilleur que l'autre. Mon effort. J'ai recommencé. Tu as posé cube après cube. La tour tient. Tu veux poser le dernier cube ? Le petit, tout en haut. Amir pose le dernier cube. La tour reste debout, dans la lumière. Tu es fier de ton effort ? Oui. Fier. Pas meilleur que l'autre. On nomme l'effort. On nomme fier. Maman applaudit tout doux. Les mains font un petit bruit. J'ai recommencé. La tour tient. Oui. C'est ça, l'effort. On range le dernier cube, après ? Encore un moment. Elle est belle. Elle est belle, oui. Ton effort aussi. Le cube rouge est en bas. Tu l'as vu ? Oui. Le bleu est au milieu. Tu as choisi. Cube après cube. Le rond de lumière reste sur le tapis. Le panier en osier attend à côté. Un cube resté dedans tapote un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1353,7 +1353,6 @@
 maman|Fier de ton effort.
 maman|Pas meilleur que l'autre.
 enfant-m|Mon effort. J'ai recommencé.
-maman|Bravo, Amir. C'est du bon travail.
 maman|Tu as posé cube après cube.
 enfant-m|La tour tient.
 maman|Tu veux poser le dernier cube ?
@@ -1412,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La tour tient. Quelle émotion ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tour tient. Quelle émotion ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1567,7 +1566,6 @@
 narrateur|Quelle émotion ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a nommé : fier. C'était son effort. Je suis fier de mon effort. Oui. Tu as recommencé. Pas meilleur que l'autre. Bravo. C'est du bon travail. La tour tient. Mon effort. Tu veux encore dire le mot ? Fier. Le dernier cube reste en haut. Le bois est lisse sous les doigts.</t>
+          <t>Amir a nommé : fier. C'était son effort. Je suis fier de mon effort. Oui. Tu as recommencé. Pas meilleur que l'autre. La tour tient. Mon effort. Tu veux encore dire le mot ? Fier. Le dernier cube reste en haut. Le bois est lisse sous les doigts.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam a dit : je suis &lt;emphasis level="moderate"&gt;fier&lt;/emphasis&gt;. C'était son effort.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a nommé : fier. C'était son effort. Je suis fier de mon effort. Oui. Tu as recommencé. Pas meilleur que l'autre. La tour tient. Mon effort. Tu veux encore dire le mot ? Fier. Le dernier cube reste en haut. Le bois est lisse sous les doigts.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1741,7 +1739,6 @@
 enfant-m|Je suis fier de mon effort.
 maman|Oui. Tu as recommencé.
 maman|Pas meilleur que l'autre.
-maman|Bravo. C'est du bon travail.
 enfant-m|La tour tient. Mon effort.
 maman|Tu veux encore dire le mot ?
 enfant-m|Fier.
@@ -1783,7 +1780,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman baisse la lumière. Adam souffle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman baisse un peu la lumière. Tu souffles, Amir ? Oui. La tour reste debout. On la laisse jusqu'au dîner ? Oui. Je suis encore fier. Bravo. Ton effort est là. Amir souffle. Le panier en osier est calme. Les cubes restés dedans ne bougent plus.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1954,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais fier de mon effort. Tu as recommencé. Bravo. La tour reste debout, tout doux. L'histoire est finie.</t>
+          <t>J'étais fier de mon effort. Tu as recommencé. Bravo. La tour reste debout, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais fier de mon effort. Tu as recommencé. Bravo. La tour reste debout, tout doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2096,11 +2093,9 @@
         <is>
           <t>enfant-m|J'étais fier de mon effort.
 maman|Tu as recommencé. Bravo.
-narrateur|La tour reste debout, tout doux.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La tour reste debout, tout doux.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2119,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.010-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adam, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
